--- a/public_html/assets/archivo/corte/10-NUTRICION/10-NUTRICION_33-2024_02.xlsx
+++ b/public_html/assets/archivo/corte/10-NUTRICION/10-NUTRICION_33-2024_02.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="53">
   <si>
     <t>PAGO</t>
   </si>
@@ -28,9 +28,6 @@
     <t>SOCIO</t>
   </si>
   <si>
-    <t>RFC</t>
-  </si>
-  <si>
     <t>CLABE</t>
   </si>
   <si>
@@ -55,89 +52,141 @@
     <t>DESCRIPCIÓN</t>
   </si>
   <si>
+    <t xml:space="preserve">RENE JAVIER MEDRANO LOPEZ  </t>
+  </si>
+  <si>
+    <t>012650028495052889</t>
+  </si>
+  <si>
+    <t>PAGO SEMANA 33-2024</t>
+  </si>
+  <si>
+    <t>DEL 12 DE AGOSTO AL 18 DE AGOSTO</t>
+  </si>
+  <si>
+    <t>PAGO DE COMISIONES</t>
+  </si>
+  <si>
     <t xml:space="preserve">HECTOR JAVIER ARMANDO RODRIGUEZ VALDES  </t>
   </si>
   <si>
     <t>002420903527668862</t>
   </si>
   <si>
-    <t>PAGO SEMANA 33-2024</t>
+    <t>LUCINA MARIA AURORA  RODRIGUEZ  MERIDA</t>
+  </si>
+  <si>
+    <t>012580028886932853</t>
+  </si>
+  <si>
+    <t>GERARDO DANIEL   HERMIDA AMADOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MA GUADALUPE VAZQUEZ FLORES  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOFIA BARROSO RUIZ  </t>
+  </si>
+  <si>
+    <t>012261004726315475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAIME GOMEZ SERRA  </t>
+  </si>
+  <si>
+    <t>MARIA DE LA LUZ  MUÑOZ  CASTELLANOS</t>
+  </si>
+  <si>
+    <t>012320029389721173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PATRICIA ALCOCER CARVAJAL  </t>
+  </si>
+  <si>
+    <t>012261015561538956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUEL DE JESUS CASTALDI PEREZ  </t>
+  </si>
+  <si>
+    <t>BENEFICIARIO</t>
+  </si>
+  <si>
+    <t>IMPORTE</t>
+  </si>
+  <si>
+    <t>RET DE IVA 10.66%</t>
+  </si>
+  <si>
+    <t>IVA 16%</t>
+  </si>
+  <si>
+    <t>CONCEPTO DE FACTURA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BENJAMIN RAUL PADILLA BARRAGÁN  </t>
+  </si>
+  <si>
+    <t>002528700329964759</t>
   </si>
   <si>
     <t>BANAMEX</t>
   </si>
   <si>
-    <t>DEL 12 DE AGOSTO AL 18 DE AGOSTO</t>
-  </si>
-  <si>
-    <t>GERARDO DANIEL   HERMIDA AMADOR</t>
-  </si>
-  <si>
-    <t>AZTECA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOFIA BARROSO RUIZ  </t>
-  </si>
-  <si>
-    <t>012261004726315475</t>
+    <t>IGNACIO  ALCOCER  CARVAJAL</t>
+  </si>
+  <si>
+    <t>012261011384032604</t>
   </si>
   <si>
     <t>BBVA MEXICO</t>
   </si>
   <si>
-    <t>MARIA DE LA LUZ  MUÑOZ  CASTELLANOS</t>
-  </si>
-  <si>
-    <t>012320029389721173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANUEL DE JESUS CASTALDI PEREZ  </t>
-  </si>
-  <si>
-    <t>BENEFICIARIO</t>
-  </si>
-  <si>
-    <t>IMPORTE</t>
-  </si>
-  <si>
-    <t>RETENCIÓN DE IVA 10.66%</t>
-  </si>
-  <si>
-    <t>IVA 16%</t>
-  </si>
-  <si>
-    <t>CONCEPTO DE FACTURA</t>
+    <t>EUGENIA  ALCOCER  CARVAJAL</t>
+  </si>
+  <si>
+    <t>012261015099257013</t>
+  </si>
+  <si>
+    <t>CODIGO SAT</t>
+  </si>
+  <si>
+    <t>CONCEPTO FACTURA</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>DESC. BONIF. P-P BENELEIT</t>
+  </si>
+  <si>
+    <t>NETO</t>
+  </si>
+  <si>
+    <t>IVA</t>
+  </si>
+  <si>
+    <t>RET 1.25%</t>
+  </si>
+  <si>
+    <t>PROMOCIÓN, DISPOSICIÓN Y PUBLICIDAD VENTAS BENELEIT</t>
   </si>
   <si>
     <t xml:space="preserve">LUIS ALBERTO LIN SALINAS  </t>
   </si>
   <si>
-    <t>LISL720802GW9</t>
-  </si>
-  <si>
     <t>012180015558104539</t>
-  </si>
-  <si>
-    <t>IGNACIO  ALCOCER  CARVAJAL</t>
-  </si>
-  <si>
-    <t>AOCI730717A95</t>
-  </si>
-  <si>
-    <t>012261011384032604</t>
-  </si>
-  <si>
-    <t>1,122.25</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#"/>
+    <numFmt numFmtId="165" formatCode="$#,##0.00"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <b val="0"/>
       <i val="0"/>
@@ -147,13 +196,34 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="11"/>
+      <color rgb="FFffffff"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF009779"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF192b5a"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -168,9 +238,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="10">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="0" numFmtId="164" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="164" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="165" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="164" fillId="2" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="165" fillId="3" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="165" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="165" fillId="3" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -470,234 +560,467 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="5.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="6.998" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="9.283" bestFit="true" customWidth="true" style="1"/>
+    <col min="2" max="2" width="9.283" bestFit="true" customWidth="true" style="1"/>
     <col min="3" max="3" width="48.274" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="22.28" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="6.998" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="23.423" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="19.995" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="6.998" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="10.569" bestFit="true" customWidth="true" style="1"/>
-    <col min="10" max="10" width="11.711" bestFit="true" customWidth="true" style="1"/>
-    <col min="11" max="11" width="38.848" bestFit="true" customWidth="true" style="1"/>
-    <col min="12" max="12" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="24.565" bestFit="true" customWidth="true" style="2"/>
+    <col min="5" max="5" width="17.567" bestFit="true" customWidth="true" style="1"/>
+    <col min="6" max="6" width="25.708" bestFit="true" customWidth="true" style="1"/>
+    <col min="7" max="7" width="20.995" bestFit="true" customWidth="true" style="1"/>
+    <col min="8" max="8" width="11.711" bestFit="true" customWidth="true" style="3"/>
+    <col min="9" max="9" width="9.283" bestFit="true" customWidth="true" style="3"/>
+    <col min="10" max="10" width="9.283" bestFit="true" customWidth="true" style="3"/>
+    <col min="11" max="11" width="18.71" bestFit="true" customWidth="true" style="0"/>
+    <col min="12" max="12" width="38.848" bestFit="true" customWidth="true" style="0"/>
+    <col min="13" max="13" width="22.28" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" t="s">
+    <row r="1" spans="1:13">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1">
+        <v>11574</v>
+      </c>
+      <c r="B2" s="1">
+        <v>92</v>
+      </c>
+      <c r="C2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2">
-        <v>5866</v>
-      </c>
-      <c r="B2">
+      <c r="D2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="1">
+        <v>30</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1131.7327586207</v>
+      </c>
+      <c r="H2" s="3">
+        <v>1312.81</v>
+      </c>
+      <c r="I2" s="3">
+        <v>120.64271206897</v>
+      </c>
+      <c r="J2" s="3">
+        <v>181.07724137931</v>
+      </c>
+      <c r="K2">
+        <v>1192.167287931</v>
+      </c>
+      <c r="L2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1">
+        <v>11577</v>
+      </c>
+      <c r="B3" s="1">
         <v>11101</v>
       </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="1">
+        <v>30</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E2">
-        <v>30</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="G3" s="1">
+        <v>581.89655172414</v>
+      </c>
+      <c r="H3" s="3">
+        <v>675.0</v>
+      </c>
+      <c r="I3" s="3">
+        <v>62.030172413793</v>
+      </c>
+      <c r="J3" s="3">
+        <v>93.103448275862</v>
+      </c>
+      <c r="K3">
+        <v>612.96982758621</v>
+      </c>
+      <c r="L3" t="s">
         <v>14</v>
       </c>
-      <c r="G2" t="s">
+      <c r="M3" t="s">
         <v>15</v>
       </c>
-      <c r="H2">
-        <v>600.0</v>
-      </c>
-      <c r="I2" s="1">
-        <v>30.7</v>
-      </c>
-      <c r="J2" s="1">
-        <v>569.3</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3">
-        <v>5864</v>
-      </c>
-      <c r="B3">
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1">
+        <v>11611</v>
+      </c>
+      <c r="B4" s="1">
+        <v>15432</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="1">
+        <v>30</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="1">
+        <v>129.31034482759</v>
+      </c>
+      <c r="H4" s="3">
+        <v>150.0</v>
+      </c>
+      <c r="I4" s="3">
+        <v>13.784482758621</v>
+      </c>
+      <c r="J4" s="3">
+        <v>20.689655172414</v>
+      </c>
+      <c r="K4">
+        <v>136.21551724138</v>
+      </c>
+      <c r="L4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1">
+        <v>11575</v>
+      </c>
+      <c r="B5" s="1">
         <v>17042</v>
       </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3">
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="2">
         <v>127290013759479947</v>
       </c>
-      <c r="E3">
-        <v>30</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="E5" s="1">
+        <v>30</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="1">
+        <v>64.655172413793</v>
+      </c>
+      <c r="H5" s="3">
+        <v>75.0</v>
+      </c>
+      <c r="I5" s="3">
+        <v>6.8922413793103</v>
+      </c>
+      <c r="J5" s="3">
+        <v>10.344827586207</v>
+      </c>
+      <c r="K5">
+        <v>68.10775862069</v>
+      </c>
+      <c r="L5" t="s">
         <v>14</v>
       </c>
-      <c r="G3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3">
-        <v>75.0</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1.44</v>
-      </c>
-      <c r="J3" s="1">
-        <v>73.56</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4">
-        <v>5869</v>
-      </c>
-      <c r="B4">
+      <c r="M5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1">
+        <v>11579</v>
+      </c>
+      <c r="B6" s="1">
+        <v>25919</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="2">
+        <v>127528013932219641</v>
+      </c>
+      <c r="E6" s="1">
+        <v>30</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="1">
+        <v>81.077586206897</v>
+      </c>
+      <c r="H6" s="3">
+        <v>94.05</v>
+      </c>
+      <c r="I6" s="3">
+        <v>8.6428706896552</v>
+      </c>
+      <c r="J6" s="3">
+        <v>12.972413793103</v>
+      </c>
+      <c r="K6">
+        <v>85.407129310345</v>
+      </c>
+      <c r="L6" t="s">
+        <v>14</v>
+      </c>
+      <c r="M6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1">
+        <v>11590</v>
+      </c>
+      <c r="B7" s="1">
         <v>28842</v>
       </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4">
-        <v>30</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="1">
+        <v>30</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1403.4482758621</v>
+      </c>
+      <c r="H7" s="3">
+        <v>1628.0</v>
+      </c>
+      <c r="I7" s="3">
+        <v>149.6075862069</v>
+      </c>
+      <c r="J7" s="3">
+        <v>224.55172413793</v>
+      </c>
+      <c r="K7">
+        <v>1478.3924137931</v>
+      </c>
+      <c r="L7" t="s">
         <v>14</v>
       </c>
-      <c r="G4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4">
-        <v>2836.0</v>
-      </c>
-      <c r="I4" s="1">
-        <v>249.58</v>
-      </c>
-      <c r="J4" s="1">
-        <v>2586.42</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5">
-        <v>5884</v>
-      </c>
-      <c r="B5">
+      <c r="M7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1">
+        <v>11619</v>
+      </c>
+      <c r="B8" s="1">
+        <v>31624</v>
+      </c>
+      <c r="C8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="2">
+        <v>127854001413020886</v>
+      </c>
+      <c r="E8" s="1">
+        <v>30</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="1">
+        <v>74.310344827586</v>
+      </c>
+      <c r="H8" s="3">
+        <v>86.2</v>
+      </c>
+      <c r="I8" s="3">
+        <v>7.9214827586207</v>
+      </c>
+      <c r="J8" s="3">
+        <v>11.889655172414</v>
+      </c>
+      <c r="K8">
+        <v>78.278517241379</v>
+      </c>
+      <c r="L8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1">
+        <v>11601</v>
+      </c>
+      <c r="B9" s="1">
         <v>33949</v>
       </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5">
-        <v>30</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="1">
+        <v>30</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="1">
+        <v>366.37931034483</v>
+      </c>
+      <c r="H9" s="3">
+        <v>425.0</v>
+      </c>
+      <c r="I9" s="3">
+        <v>39.056034482759</v>
+      </c>
+      <c r="J9" s="3">
+        <v>58.620689655172</v>
+      </c>
+      <c r="K9">
+        <v>385.94396551724</v>
+      </c>
+      <c r="L9" t="s">
         <v>14</v>
       </c>
-      <c r="G5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5">
-        <v>325.0</v>
-      </c>
-      <c r="I5" s="1">
-        <v>13.1</v>
-      </c>
-      <c r="J5" s="1">
-        <v>311.9</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6">
-        <v>5891</v>
-      </c>
-      <c r="B6">
+      <c r="M9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1">
+        <v>11583</v>
+      </c>
+      <c r="B10" s="1">
+        <v>41929</v>
+      </c>
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="1">
+        <v>30</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1331.4224137931</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1544.45</v>
+      </c>
+      <c r="I10" s="3">
+        <v>141.92962931034</v>
+      </c>
+      <c r="J10" s="3">
+        <v>213.0275862069</v>
+      </c>
+      <c r="K10">
+        <v>1402.5203706897</v>
+      </c>
+      <c r="L10" t="s">
+        <v>14</v>
+      </c>
+      <c r="M10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="1">
+        <v>11610</v>
+      </c>
+      <c r="B11" s="1">
         <v>46264</v>
       </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6">
+      <c r="C11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="2">
         <v>127131013606487141</v>
       </c>
-      <c r="E6">
-        <v>30</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="E11" s="1">
+        <v>30</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="1">
+        <v>387.93103448276</v>
+      </c>
+      <c r="H11" s="3">
+        <v>450.0</v>
+      </c>
+      <c r="I11" s="3">
+        <v>41.353448275862</v>
+      </c>
+      <c r="J11" s="3">
+        <v>62.068965517241</v>
+      </c>
+      <c r="K11">
+        <v>408.64655172414</v>
+      </c>
+      <c r="L11" t="s">
         <v>14</v>
       </c>
-      <c r="G6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6">
-        <v>450.0</v>
-      </c>
-      <c r="I6" s="1">
-        <v>21.1</v>
-      </c>
-      <c r="J6" s="1">
-        <v>428.9</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>16</v>
+      <c r="M11" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -712,139 +1035,159 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="5.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="6.998" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="31.707" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="16.425" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="22.28" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="19.995" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="23.423" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="13.997" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="28.136" bestFit="true" customWidth="true" style="1"/>
-    <col min="10" max="10" width="9.283" bestFit="true" customWidth="true" style="1"/>
-    <col min="11" max="11" width="10.569" bestFit="true" customWidth="true" style="1"/>
-    <col min="12" max="12" width="38.848" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="9.283" bestFit="true" customWidth="true" style="1"/>
+    <col min="2" max="2" width="9.283" bestFit="true" customWidth="true" style="1"/>
+    <col min="3" max="3" width="38.848" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="23.423" bestFit="true" customWidth="true" style="2"/>
+    <col min="5" max="5" width="17.567" bestFit="true" customWidth="true" style="1"/>
+    <col min="6" max="6" width="25.708" bestFit="true" customWidth="true" style="1"/>
+    <col min="7" max="7" width="16.282" bestFit="true" customWidth="true" style="8"/>
+    <col min="8" max="8" width="11.711" bestFit="true" customWidth="true" style="3"/>
+    <col min="9" max="9" width="21.138" bestFit="true" customWidth="true" style="3"/>
+    <col min="10" max="10" width="11.711" bestFit="true" customWidth="true" style="3"/>
+    <col min="11" max="11" width="38.848" bestFit="true" customWidth="true" style="3"/>
+    <col min="12" max="12" width="13.997" bestFit="true" customWidth="true" style="0"/>
     <col min="13" max="13" width="23.423" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="C1" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="G1" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>29</v>
+      <c r="M1" s="5" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2">
-        <v>5875</v>
-      </c>
-      <c r="B2">
-        <v>15862</v>
+      <c r="A2" s="1">
+        <v>11580</v>
+      </c>
+      <c r="B2" s="1">
+        <v>25918</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F2">
-        <v>30</v>
-      </c>
-      <c r="G2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" s="1">
+        <v>30</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2" s="3">
+        <v>908.08</v>
+      </c>
+      <c r="J2" s="3">
+        <v>908.08</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" s="1">
-        <v>312.5</v>
-      </c>
-      <c r="J2" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="K2" s="1">
-        <v>312.5</v>
-      </c>
-      <c r="L2" t="s">
-        <v>16</v>
-      </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3">
-        <v>5868</v>
-      </c>
-      <c r="B3">
+      <c r="A3" s="1">
+        <v>11582</v>
+      </c>
+      <c r="B3" s="1">
         <v>32605</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F3">
-        <v>30</v>
-      </c>
-      <c r="G3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="1">
+        <v>30</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3" s="3">
+        <v>872.75</v>
+      </c>
+      <c r="J3" s="3">
+        <v>872.75</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="J3" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="L3" t="s">
-        <v>16</v>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1">
+        <v>11581</v>
+      </c>
+      <c r="B4" s="1">
+        <v>32614</v>
+      </c>
+      <c r="C4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="1">
+        <v>30</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H4" s="3">
+        <v>1080.0</v>
+      </c>
+      <c r="J4" s="3">
+        <v>1080.0</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -859,55 +1202,125 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="5.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="3.428" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="6.998" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="6.998" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="15.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="19.995" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="6.998" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="10.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="4.57" bestFit="true" customWidth="true" style="1"/>
-    <col min="10" max="10" width="6.998" bestFit="true" customWidth="true" style="1"/>
-    <col min="11" max="11" width="13.997" bestFit="true" customWidth="true" style="1"/>
+    <col min="1" max="1" width="9.283" bestFit="true" customWidth="true" style="1"/>
+    <col min="2" max="2" width="15.139" bestFit="true" customWidth="true" style="1"/>
+    <col min="3" max="3" width="63.556" bestFit="true" customWidth="true" style="1"/>
+    <col min="4" max="4" width="9.283" bestFit="true" customWidth="true" style="1"/>
+    <col min="5" max="5" width="31.707" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="23.423" bestFit="true" customWidth="true" style="2"/>
+    <col min="7" max="7" width="17.567" bestFit="true" customWidth="true" style="1"/>
+    <col min="8" max="8" width="25.708" bestFit="true" customWidth="true" style="1"/>
+    <col min="9" max="9" width="30.564" bestFit="true" customWidth="true" style="3"/>
+    <col min="10" max="10" width="9.283" bestFit="true" customWidth="true" style="3"/>
+    <col min="11" max="11" width="9.283" bestFit="true" customWidth="true" style="3"/>
+    <col min="12" max="12" width="10.569" bestFit="true" customWidth="true" style="3"/>
+    <col min="13" max="13" width="8.141" bestFit="true" customWidth="true" style="3"/>
+    <col min="14" max="14" width="11.711" bestFit="true" customWidth="true" style="3"/>
+    <col min="15" max="15" width="9.283" bestFit="true" customWidth="true" style="3"/>
+    <col min="16" max="16" width="38.848" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" t="s">
+    <row r="1" spans="1:16">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="I1" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="L1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="H1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="M1" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="O1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="P1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>11</v>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="1">
+        <v>11588</v>
+      </c>
+      <c r="B2" s="1">
+        <v>80161701</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="1">
+        <v>15862</v>
+      </c>
+      <c r="E2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G2" s="1">
+        <v>30</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="3">
+        <v>35.560344827586</v>
+      </c>
+      <c r="J2" s="3">
+        <v>412.5</v>
+      </c>
+      <c r="K2" s="3">
+        <v>355.60344827586</v>
+      </c>
+      <c r="L2" s="3">
+        <v>320.04310344828</v>
+      </c>
+      <c r="M2" s="3">
+        <v>51.206896551724</v>
+      </c>
+      <c r="N2" s="3">
+        <v>4.0005387931034</v>
+      </c>
+      <c r="O2" s="3">
+        <v>424.14601293103</v>
+      </c>
+      <c r="P2" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
